--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R98ebc9e9cf144fda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R33d24d71bd424b92"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R33d24d71bd424b92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd97b39d1666f463d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd97b39d1666f463d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc3c5ad0812b940b7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc3c5ad0812b940b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R51ea01e7fb2749b8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R51ea01e7fb2749b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4212d682697a417f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4212d682697a417f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra9417117df7b4499"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra9417117df7b4499"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R83a5e602588745b2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R83a5e602588745b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R374b2217942b44e7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R374b2217942b44e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0f4828fdc71e4375"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0f4828fdc71e4375"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb85df9ba2ad04d64"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb85df9ba2ad04d64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1e834e0180924415"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1e834e0180924415"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R60fc42ebe51843f9"/>
   </x:sheets>
 </x:workbook>
 </file>
